--- a/backend/excel-templates/master_upload_template.xlsx
+++ b/backend/excel-templates/master_upload_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,105 +415,35 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Elina Maskey</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>080MECE001</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>Sample Master Thesis 1</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>2081</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Firoj Ansari</v>
+        <v>Anup Baral</v>
       </c>
       <c r="B3" t="str">
-        <v>080MECE002</v>
+        <v>080MSCS001</v>
       </c>
       <c r="C3" t="str">
-        <v>Sample Master Thesis 2</v>
+        <v>Sample Master Thesis 1</v>
       </c>
       <c r="D3" t="str">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Gita Neupane</v>
-      </c>
-      <c r="B4" t="str">
-        <v>080MPED001</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Sample Master Thesis 3</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Anup Baral</v>
-      </c>
-      <c r="B5" t="str">
-        <v>080MSCS001</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Sample Master Thesis 4</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Bhawana Sapkota</v>
-      </c>
-      <c r="B6" t="str">
-        <v>080MSCS002</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Sample Master Thesis 5</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Dinesh Parajuli</v>
-      </c>
-      <c r="B7" t="str">
-        <v>080MSCS003</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Sample Master Thesis 6</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Mast Student</v>
-      </c>
-      <c r="B8" t="str">
-        <v>080MSCS099</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Sample Master Thesis 7</v>
-      </c>
-      <c r="D8" t="str">
         <v>2081</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/excel-templates/master_upload_template.xlsx
+++ b/backend/excel-templates/master_upload_template.xlsx
@@ -397,20 +397,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:I4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Student Name</v>
+        <v>Name</v>
       </c>
       <c r="B1" t="str">
-        <v>Roll Number</v>
+        <v>Roll</v>
       </c>
       <c r="C1" t="str">
-        <v>Thesis Title</v>
+        <v>Title</v>
       </c>
       <c r="D1" t="str">
-        <v>Academic Year</v>
+        <v>Batch</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Cluster</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Program</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Supervisor</v>
+      </c>
+      <c r="H1" t="str">
+        <v>External_mid_term</v>
+      </c>
+      <c r="I1" t="str">
+        <v>External_final</v>
       </c>
     </row>
     <row r="2">
@@ -424,6 +439,21 @@
         <v/>
       </c>
       <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v/>
       </c>
     </row>
@@ -435,15 +465,59 @@
         <v>080MSCS001</v>
       </c>
       <c r="C3" t="str">
-        <v>Sample Master Thesis 1</v>
+        <v>Deep Learning for Nepali Sign Language Recognition</v>
       </c>
       <c r="D3" t="str">
-        <v>2081</v>
+        <v>080</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Cluster 1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>MSc in Network and Cyber Security</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Dr. Ram Acharya</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Prof. Sita Sharma</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Dr. Hari Basnet</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Bina Thapa</v>
+      </c>
+      <c r="B4" t="str">
+        <v>080MSDSA001</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Predictive Analytics for Agricultural Yield in Nepal</v>
+      </c>
+      <c r="D4" t="str">
+        <v>080</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Cluster 3</v>
+      </c>
+      <c r="F4" t="str">
+        <v>MSc in Data Science and Analytics</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Prof. Krishna Poudel</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Dr. Gita Rai</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Prof. Mohan Adhikari</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/excel-templates/master_upload_template.xlsx
+++ b/backend/excel-templates/master_upload_template.xlsx
@@ -462,7 +462,7 @@
         <v>Anup Baral</v>
       </c>
       <c r="B3" t="str">
-        <v>080MSCS001</v>
+        <v>080MSCS01</v>
       </c>
       <c r="C3" t="str">
         <v>Deep Learning for Nepali Sign Language Recognition</v>
@@ -491,7 +491,7 @@
         <v>Bina Thapa</v>
       </c>
       <c r="B4" t="str">
-        <v>080MSDSA001</v>
+        <v>080MSDSA01</v>
       </c>
       <c r="C4" t="str">
         <v>Predictive Analytics for Agricultural Yield in Nepal</v>

--- a/backend/excel-templates/master_upload_template.xlsx
+++ b/backend/excel-templates/master_upload_template.xlsx
@@ -397,7 +397,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,10 +433,10 @@
         <v>Supervisor</v>
       </c>
       <c r="H1" t="str">
-        <v>External_mid_term</v>
+        <v>External Mid Term</v>
       </c>
       <c r="I1" t="str">
-        <v>External_final</v>
+        <v>External Final</v>
       </c>
     </row>
     <row r="2">
@@ -459,13 +470,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Anup Baral</v>
+        <v>Ram Dahal</v>
       </c>
       <c r="B3" t="str">
-        <v>080MSCS01</v>
+        <v>080MSNCS01</v>
       </c>
       <c r="C3" t="str">
-        <v>Deep Learning for Nepali Sign Language Recognition</v>
+        <v>Machine Learning for Early Detection of Crop Diseases</v>
       </c>
       <c r="D3" t="str">
         <v>080</v>
@@ -477,47 +488,18 @@
         <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G3" t="str">
-        <v>Dr. Ram Acharya</v>
+        <v>Prof. Dr. Rajan Sharma</v>
       </c>
       <c r="H3" t="str">
-        <v>Prof. Sita Sharma</v>
+        <v>Prof. Dr. Hari Bhandari</v>
       </c>
       <c r="I3" t="str">
-        <v>Dr. Hari Basnet</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Bina Thapa</v>
-      </c>
-      <c r="B4" t="str">
-        <v>080MSDSA01</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Predictive Analytics for Agricultural Yield in Nepal</v>
-      </c>
-      <c r="D4" t="str">
-        <v>080</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Cluster 3</v>
-      </c>
-      <c r="F4" t="str">
-        <v>MSc in Data Science and Analytics</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Prof. Krishna Poudel</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Dr. Gita Rai</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Prof. Mohan Adhikari</v>
+        <v>Dr. Sagar Ojha</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/excel-templates/master_upload_template.xlsx
+++ b/backend/excel-templates/master_upload_template.xlsx
@@ -397,18 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,10 +422,10 @@
         <v>Supervisor</v>
       </c>
       <c r="H1" t="str">
-        <v>External Mid Term</v>
+        <v>External_mid_term</v>
       </c>
       <c r="I1" t="str">
-        <v>External Final</v>
+        <v>External_final</v>
       </c>
     </row>
     <row r="2">
@@ -470,13 +459,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Ram Dahal</v>
+        <v>Anup Baral</v>
       </c>
       <c r="B3" t="str">
-        <v>080MSNCS01</v>
+        <v>080MSCS01</v>
       </c>
       <c r="C3" t="str">
-        <v>Machine Learning for Early Detection of Crop Diseases</v>
+        <v>Deep Learning for Nepali Sign Language Recognition</v>
       </c>
       <c r="D3" t="str">
         <v>080</v>
@@ -488,18 +477,47 @@
         <v>MSc in Network and Cyber Security</v>
       </c>
       <c r="G3" t="str">
-        <v>Prof. Dr. Rajan Sharma</v>
+        <v>Dr. Ram Acharya</v>
       </c>
       <c r="H3" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Prof. Sita Sharma</v>
       </c>
       <c r="I3" t="str">
-        <v>Dr. Sagar Ojha</v>
+        <v>Dr. Hari Basnet</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Bina Thapa</v>
+      </c>
+      <c r="B4" t="str">
+        <v>080MSDSA01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Predictive Analytics for Agricultural Yield in Nepal</v>
+      </c>
+      <c r="D4" t="str">
+        <v>080</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Cluster 3</v>
+      </c>
+      <c r="F4" t="str">
+        <v>MSc in Data Science and Analytics</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Prof. Krishna Poudel</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Dr. Gita Rai</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Prof. Mohan Adhikari</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>
 </worksheet>
 </file>